--- a/Tables/G_RewardInfoTable.xlsx
+++ b/Tables/G_RewardInfoTable.xlsx
@@ -363,7 +363,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="8" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="10.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="10.88"/>
+    <col customWidth="1" min="6" max="6" width="11.88"/>
+    <col customWidth="1" min="7" max="7" width="11.25"/>
+    <col customWidth="1" min="8" max="8" width="11.38"/>
+    <col customWidth="1" min="9" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6566,7 +6574,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="8" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="10.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="10.88"/>
+    <col customWidth="1" min="6" max="6" width="11.88"/>
+    <col customWidth="1" min="7" max="7" width="11.25"/>
+    <col customWidth="1" min="8" max="8" width="11.38"/>
+    <col customWidth="1" min="9" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12769,7 +12785,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="8" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="12.0"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="10.88"/>
+    <col customWidth="1" min="6" max="6" width="11.88"/>
+    <col customWidth="1" min="7" max="7" width="11.25"/>
+    <col customWidth="1" min="8" max="8" width="11.38"/>
+    <col customWidth="1" min="9" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18972,7 +18996,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="8" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="12.0"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="10.88"/>
+    <col customWidth="1" min="6" max="6" width="11.88"/>
+    <col customWidth="1" min="7" max="7" width="11.25"/>
+    <col customWidth="1" min="8" max="8" width="11.38"/>
+    <col customWidth="1" min="9" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25175,7 +25207,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="8" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="10.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="10.88"/>
+    <col customWidth="1" min="6" max="6" width="11.88"/>
+    <col customWidth="1" min="7" max="7" width="11.25"/>
+    <col customWidth="1" min="8" max="8" width="11.38"/>
+    <col customWidth="1" min="9" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31379,7 +31419,14 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="13.5"/>
-    <col customWidth="1" min="2" max="8" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="10.88"/>
+    <col customWidth="1" min="6" max="6" width="11.88"/>
+    <col customWidth="1" min="7" max="7" width="11.25"/>
+    <col customWidth="1" min="8" max="8" width="11.38"/>
+    <col customWidth="1" min="9" max="26" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
